--- a/noles_in_the_pros_updated.xlsx
+++ b/noles_in_the_pros_updated.xlsx
@@ -1604,12 +1604,12 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Low-A</t>
+          <t>High-A</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Fredericksburg Nationals</t>
+          <t>Wilmington Blue Rocks</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
@@ -1626,7 +1626,7 @@
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2024 14th-round pick</t>
+          <t>2024 14th-round pick; promoted to High-A Wilmington Blue Rocks (Washington Nationals) in 2026; 3.80 ERA, 42.2 IP, 43 K, 1.27 WHIP</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
